--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7593" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7593" uniqueCount="565">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T05:36:05+00:00</t>
+    <t>2026-07-29T08:04:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -462,9 +462,6 @@
     <t>ccdPlanOfCareActivityPlanned</t>
   </si>
   <si>
-    <t xml:space="preserve">Conformité Plan of care activity (CCD) si acte prévu </t>
-  </si>
-  <si>
     <t>Conformité Plan of care activity (CCD) si acte prévu</t>
   </si>
   <si>
@@ -492,9 +489,6 @@
     <t>ccdPlanOfCareActivityPlannedRealised</t>
   </si>
   <si>
-    <t xml:space="preserve">Conformité Procedure activity (CCD) si acte réalisée </t>
-  </si>
-  <si>
     <t>Conformité Procedure activity (CCD) si acte réalisée</t>
   </si>
   <si>
@@ -559,9 +553,9 @@
   </si>
   <si>
     <t>- Si acte prévu : moodCode='INT' ; negationInd='false' (valeur par défaut) 
-- Si acte réalisé : moodCode='EVN' ; negationInd='true' 
-    - si l'acte n'a pas eu lieu : negationInd='false' 
-    - si l'acte a eu lieu (valeur par défaut)</t>
+ - Si acte réalisé : moodCode='EVN' ; negationInd='true' 
+     - si l'acte n'a pas eu lieu : negationInd='false' 
+     - si l'acte a eu lieu (valeur par défaut)</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-xDocumentProcedureMood|3.0.0</t>
@@ -916,7 +910,7 @@
     <t>Procedure.languageCode</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/all-languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Procedure.methodCode</t>
@@ -966,7 +960,7 @@
     <t>Procedure.approachSiteCode.qualifier</t>
   </si>
   <si>
-    <t xml:space="preserve">Latéralité SNOMED CT (2.16.840.1.113883.6.96) </t>
+    <t>Latéralité SNOMED CT (2.16.840.1.113883.6.96)</t>
   </si>
   <si>
     <t>Latéralité</t>
@@ -3922,7 +3916,7 @@
         <v>145</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3993,7 +3987,7 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B19" t="s" s="2">
         <v>132</v>
@@ -4094,7 +4088,7 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>134</v>
@@ -4197,7 +4191,7 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>136</v>
@@ -4300,7 +4294,7 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s" s="2">
         <v>138</v>
@@ -4344,7 +4338,7 @@
         <v>75</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>75</v>
@@ -4403,7 +4397,7 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>142</v>
@@ -4506,13 +4500,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>75</v>
@@ -4537,10 +4531,10 @@
         <v>96</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4611,7 +4605,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>132</v>
@@ -4712,7 +4706,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>134</v>
@@ -4815,7 +4809,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>136</v>
@@ -4918,7 +4912,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>138</v>
@@ -4962,7 +4956,7 @@
         <v>75</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>75</v>
@@ -5021,7 +5015,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>142</v>
@@ -5124,13 +5118,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>121</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>75</v>
@@ -5155,10 +5149,10 @@
         <v>96</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5229,7 +5223,7 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B31" t="s" s="2">
         <v>132</v>
@@ -5330,7 +5324,7 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s" s="2">
         <v>134</v>
@@ -5433,7 +5427,7 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B33" t="s" s="2">
         <v>136</v>
@@ -5536,7 +5530,7 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B34" t="s" s="2">
         <v>138</v>
@@ -5580,7 +5574,7 @@
         <v>75</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>75</v>
@@ -5639,7 +5633,7 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B35" t="s" s="2">
         <v>142</v>
@@ -5742,10 +5736,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5759,7 +5753,7 @@
         <v>76</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>75</v>
@@ -5779,7 +5773,7 @@
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>75</v>
@@ -5801,7 +5795,7 @@
       </c>
       <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>75</v>
@@ -5819,7 +5813,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5839,10 +5833,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5856,7 +5850,7 @@
         <v>76</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>75</v>
@@ -5868,7 +5862,7 @@
         <v>86</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="M37" s="2"/>
       <c r="N37" s="2"/>
@@ -5900,7 +5894,7 @@
       </c>
       <c r="Y37" s="2"/>
       <c r="Z37" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>75</v>
@@ -5918,7 +5912,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5938,10 +5932,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5955,7 +5949,7 @@
         <v>82</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>75</v>
@@ -5967,10 +5961,10 @@
         <v>96</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6021,7 +6015,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6041,10 +6035,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6067,7 +6061,7 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
@@ -6120,7 +6114,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6140,10 +6134,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6157,7 +6151,7 @@
         <v>76</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>75</v>
@@ -6166,13 +6160,13 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L40" t="s" s="2">
         <v>182</v>
       </c>
-      <c r="L40" t="s" s="2">
-        <v>184</v>
-      </c>
       <c r="M40" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6223,7 +6217,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6243,10 +6237,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6344,10 +6338,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6363,7 +6357,7 @@
         <v>76</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>75</v>
@@ -6376,7 +6370,7 @@
       </c>
       <c r="L42" s="2"/>
       <c r="M42" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6427,7 +6421,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6447,17 +6441,17 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E43" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F43" t="s" s="2">
         <v>76</v>
@@ -6466,7 +6460,7 @@
         <v>76</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>75</v>
@@ -6479,7 +6473,7 @@
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6530,7 +6524,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6550,17 +6544,17 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E44" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F44" t="s" s="2">
         <v>81</v>
@@ -6582,7 +6576,7 @@
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6633,7 +6627,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -6653,17 +6647,17 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E45" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F45" t="s" s="2">
         <v>81</v>
@@ -6685,7 +6679,7 @@
       </c>
       <c r="L45" s="2"/>
       <c r="M45" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6736,7 +6730,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -6756,17 +6750,17 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E46" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F46" t="s" s="2">
         <v>81</v>
@@ -6775,7 +6769,7 @@
         <v>76</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>75</v>
@@ -6788,7 +6782,7 @@
       </c>
       <c r="L46" s="2"/>
       <c r="M46" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6839,7 +6833,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -6859,10 +6853,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6885,11 +6879,11 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L47" s="2"/>
       <c r="M47" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6940,7 +6934,7 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6960,10 +6954,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6990,7 +6984,7 @@
       </c>
       <c r="L48" s="2"/>
       <c r="M48" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7041,7 +7035,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7061,17 +7055,17 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E49" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F49" t="s" s="2">
         <v>81</v>
@@ -7089,11 +7083,11 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7144,7 +7138,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -7164,17 +7158,17 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E50" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F50" t="s" s="2">
         <v>81</v>
@@ -7192,11 +7186,11 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7247,7 +7241,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7267,17 +7261,17 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E51" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F51" t="s" s="2">
         <v>81</v>
@@ -7295,11 +7289,11 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7350,7 +7344,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7370,10 +7364,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7449,7 +7443,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -7469,10 +7463,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7486,7 +7480,7 @@
         <v>76</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>75</v>
@@ -7495,13 +7489,13 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7552,7 +7546,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -7572,10 +7566,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7673,17 +7667,17 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>81</v>
@@ -7705,7 +7699,7 @@
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7736,7 +7730,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>75</v>
@@ -7754,7 +7748,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7774,17 +7768,17 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E56" t="s" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F56" t="s" s="2">
         <v>81</v>
@@ -7802,11 +7796,11 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7857,7 +7851,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -7877,17 +7871,17 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E57" t="s" s="2">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="F57" t="s" s="2">
         <v>81</v>
@@ -7909,7 +7903,7 @@
       </c>
       <c r="L57" s="2"/>
       <c r="M57" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7940,7 +7934,7 @@
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>75</v>
@@ -7958,7 +7952,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -7978,17 +7972,17 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E58" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F58" t="s" s="2">
         <v>81</v>
@@ -8010,7 +8004,7 @@
       </c>
       <c r="L58" s="2"/>
       <c r="M58" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8061,7 +8055,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8081,17 +8075,17 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E59" t="s" s="2">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F59" t="s" s="2">
         <v>81</v>
@@ -8113,7 +8107,7 @@
       </c>
       <c r="L59" s="2"/>
       <c r="M59" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8140,11 +8134,11 @@
         <v>75</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>75</v>
@@ -8162,7 +8156,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -8182,10 +8176,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8241,7 +8235,7 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>75</v>
@@ -8259,7 +8253,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -8279,10 +8273,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8308,13 +8302,13 @@
         <v>103</v>
       </c>
       <c r="L61" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="N61" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8364,7 +8358,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -8384,17 +8378,17 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E62" t="s" s="2">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="F62" t="s" s="2">
         <v>76</v>
@@ -8403,7 +8397,7 @@
         <v>76</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>75</v>
@@ -8412,11 +8406,11 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8467,7 +8461,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -8487,17 +8481,17 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E63" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F63" t="s" s="2">
         <v>81</v>
@@ -8515,11 +8509,11 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8570,7 +8564,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -8582,7 +8576,7 @@
         <v>75</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>75</v>
@@ -8590,10 +8584,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8607,7 +8601,7 @@
         <v>76</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>75</v>
@@ -8619,10 +8613,10 @@
         <v>92</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8653,7 +8647,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>75</v>
@@ -8671,7 +8665,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -8691,10 +8685,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8708,7 +8702,7 @@
         <v>76</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>75</v>
@@ -8717,13 +8711,13 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>281</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8774,7 +8768,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -8794,10 +8788,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8820,13 +8814,13 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>283</v>
-      </c>
-      <c r="L66" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8853,11 +8847,11 @@
         <v>75</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="Y66" s="2"/>
       <c r="Z66" t="s" s="2">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>75</v>
@@ -8875,7 +8869,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -8895,10 +8889,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8954,7 +8948,7 @@
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>75</v>
@@ -8972,7 +8966,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -8992,10 +8986,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9018,11 +9012,11 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9073,7 +9067,7 @@
         <v>75</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -9093,10 +9087,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9119,13 +9113,13 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9176,7 +9170,7 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -9196,10 +9190,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9297,10 +9291,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9329,7 +9323,7 @@
       </c>
       <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9380,7 +9374,7 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -9400,17 +9394,17 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E72" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F72" t="s" s="2">
         <v>81</v>
@@ -9432,7 +9426,7 @@
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9483,7 +9477,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -9503,17 +9497,17 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>81</v>
@@ -9535,7 +9529,7 @@
       </c>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9586,7 +9580,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -9606,17 +9600,17 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>81</v>
@@ -9638,7 +9632,7 @@
       </c>
       <c r="L74" s="2"/>
       <c r="M74" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9689,7 +9683,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -9709,17 +9703,17 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F75" t="s" s="2">
         <v>81</v>
@@ -9741,7 +9735,7 @@
       </c>
       <c r="L75" s="2"/>
       <c r="M75" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9792,7 +9786,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -9812,10 +9806,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9838,11 +9832,11 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9893,7 +9887,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -9913,10 +9907,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9943,7 +9937,7 @@
       </c>
       <c r="L77" s="2"/>
       <c r="M77" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9994,7 +9988,7 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -10014,17 +10008,17 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>81</v>
@@ -10042,11 +10036,11 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10097,7 +10091,7 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -10117,17 +10111,17 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>81</v>
@@ -10136,7 +10130,7 @@
         <v>76</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>75</v>
@@ -10145,13 +10139,13 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10202,7 +10196,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -10222,17 +10216,17 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>81</v>
@@ -10250,11 +10244,11 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -10305,7 +10299,7 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -10325,10 +10319,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10351,13 +10345,13 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10408,7 +10402,7 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -10428,10 +10422,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10529,10 +10523,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10561,7 +10555,7 @@
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -10612,7 +10606,7 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -10632,17 +10626,17 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E84" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F84" t="s" s="2">
         <v>81</v>
@@ -10664,7 +10658,7 @@
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10715,7 +10709,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -10735,17 +10729,17 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E85" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F85" t="s" s="2">
         <v>81</v>
@@ -10767,7 +10761,7 @@
       </c>
       <c r="L85" s="2"/>
       <c r="M85" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10818,7 +10812,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -10838,17 +10832,17 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E86" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F86" t="s" s="2">
         <v>81</v>
@@ -10870,7 +10864,7 @@
       </c>
       <c r="L86" s="2"/>
       <c r="M86" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10921,7 +10915,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -10941,17 +10935,17 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>81</v>
@@ -10973,7 +10967,7 @@
       </c>
       <c r="L87" s="2"/>
       <c r="M87" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -11024,7 +11018,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -11044,10 +11038,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11070,11 +11064,11 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11125,7 +11119,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -11145,10 +11139,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11175,7 +11169,7 @@
       </c>
       <c r="L89" s="2"/>
       <c r="M89" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11226,7 +11220,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -11246,17 +11240,17 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E90" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F90" t="s" s="2">
         <v>81</v>
@@ -11265,7 +11259,7 @@
         <v>76</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>75</v>
@@ -11274,11 +11268,11 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L90" s="2"/>
       <c r="M90" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -11329,7 +11323,7 @@
         <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -11349,17 +11343,17 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E91" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F91" t="s" s="2">
         <v>81</v>
@@ -11368,7 +11362,7 @@
         <v>82</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>75</v>
@@ -11377,13 +11371,13 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -11434,7 +11428,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -11454,10 +11448,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11555,17 +11549,17 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E93" t="s" s="2">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F93" t="s" s="2">
         <v>81</v>
@@ -11583,11 +11577,11 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -11638,7 +11632,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -11658,10 +11652,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11677,7 +11671,7 @@
         <v>76</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>75</v>
@@ -11686,11 +11680,11 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="L94" s="2"/>
       <c r="M94" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -11741,7 +11735,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -11761,10 +11755,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11862,10 +11856,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11894,7 +11888,7 @@
       </c>
       <c r="L96" s="2"/>
       <c r="M96" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11906,7 +11900,7 @@
         <v>75</v>
       </c>
       <c r="S96" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="T96" t="s" s="2">
         <v>75</v>
@@ -11945,7 +11939,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
@@ -11965,17 +11959,17 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E97" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F97" t="s" s="2">
         <v>81</v>
@@ -11997,7 +11991,7 @@
       </c>
       <c r="L97" s="2"/>
       <c r="M97" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -12009,7 +12003,7 @@
         <v>75</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>75</v>
@@ -12048,7 +12042,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -12068,17 +12062,17 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F98" t="s" s="2">
         <v>81</v>
@@ -12100,7 +12094,7 @@
       </c>
       <c r="L98" s="2"/>
       <c r="M98" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12112,7 +12106,7 @@
         <v>75</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>75</v>
@@ -12151,7 +12145,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -12171,17 +12165,17 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E99" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F99" t="s" s="2">
         <v>81</v>
@@ -12203,7 +12197,7 @@
       </c>
       <c r="L99" s="2"/>
       <c r="M99" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -12254,7 +12248,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -12274,17 +12268,17 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F100" t="s" s="2">
         <v>81</v>
@@ -12306,7 +12300,7 @@
       </c>
       <c r="L100" s="2"/>
       <c r="M100" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -12318,7 +12312,7 @@
         <v>75</v>
       </c>
       <c r="S100" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="T100" t="s" s="2">
         <v>75</v>
@@ -12357,7 +12351,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -12377,10 +12371,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12403,11 +12397,11 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" t="s" s="2">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -12458,7 +12452,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -12478,10 +12472,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12508,7 +12502,7 @@
       </c>
       <c r="L102" s="2"/>
       <c r="M102" t="s" s="2">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -12559,7 +12553,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -12579,17 +12573,17 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F103" t="s" s="2">
         <v>81</v>
@@ -12607,11 +12601,11 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -12662,7 +12656,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -12682,17 +12676,17 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E104" t="s" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F104" t="s" s="2">
         <v>81</v>
@@ -12710,11 +12704,11 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" t="s" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12765,7 +12759,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -12785,17 +12779,17 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E105" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F105" t="s" s="2">
         <v>81</v>
@@ -12813,11 +12807,11 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L105" s="2"/>
       <c r="M105" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12868,7 +12862,7 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -12888,10 +12882,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12907,7 +12901,7 @@
         <v>76</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>75</v>
@@ -12916,13 +12910,13 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12973,7 +12967,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -12993,17 +12987,17 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F107" t="s" s="2">
         <v>81</v>
@@ -13021,11 +13015,11 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -13076,7 +13070,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -13096,10 +13090,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13122,7 +13116,7 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
@@ -13175,7 +13169,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -13195,10 +13189,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13221,7 +13215,7 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -13274,7 +13268,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -13294,10 +13288,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13320,7 +13314,7 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
@@ -13373,7 +13367,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -13393,10 +13387,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13419,7 +13413,7 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -13472,7 +13466,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -13492,10 +13486,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13518,7 +13512,7 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -13571,7 +13565,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -13591,10 +13585,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13617,7 +13611,7 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13670,7 +13664,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -13690,10 +13684,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13707,7 +13701,7 @@
         <v>82</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>75</v>
@@ -13716,7 +13710,7 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13757,7 +13751,7 @@
         <v>75</v>
       </c>
       <c r="AB114" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AC114" s="2"/>
       <c r="AD114" t="s" s="2">
@@ -13767,7 +13761,7 @@
         <v>126</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -13787,13 +13781,13 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D115" t="s" s="2">
         <v>75</v>
@@ -13815,13 +13809,13 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13872,7 +13866,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -13892,10 +13886,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13993,10 +13987,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14094,10 +14088,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14195,10 +14189,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -14296,10 +14290,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14399,10 +14393,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14502,10 +14496,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14605,10 +14599,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14708,10 +14702,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14809,10 +14803,10 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14849,7 +14843,7 @@
         <v>75</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>75</v>
@@ -14868,7 +14862,7 @@
       </c>
       <c r="Y125" s="2"/>
       <c r="Z125" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>75</v>
@@ -14886,7 +14880,7 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -14906,10 +14900,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14936,7 +14930,7 @@
       </c>
       <c r="L126" s="2"/>
       <c r="M126" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -14948,7 +14942,7 @@
         <v>75</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>75</v>
@@ -14987,7 +14981,7 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -15007,10 +15001,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15037,12 +15031,12 @@
       </c>
       <c r="L127" s="2"/>
       <c r="M127" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
@@ -15088,7 +15082,7 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -15108,10 +15102,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15187,7 +15181,7 @@
         <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -15207,10 +15201,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15233,7 +15227,7 @@
         <v>75</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" s="2"/>
@@ -15286,7 +15280,7 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -15306,10 +15300,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15332,7 +15326,7 @@
         <v>75</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
@@ -15385,7 +15379,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -15405,10 +15399,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15431,7 +15425,7 @@
         <v>75</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" s="2"/>
@@ -15484,7 +15478,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -15504,10 +15498,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15530,7 +15524,7 @@
         <v>75</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L132" s="2"/>
       <c r="M132" s="2"/>
@@ -15583,7 +15577,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
@@ -15603,10 +15597,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15629,7 +15623,7 @@
         <v>75</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L133" s="2"/>
       <c r="M133" s="2"/>
@@ -15682,7 +15676,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -15702,10 +15696,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -15728,7 +15722,7 @@
         <v>75</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" s="2"/>
@@ -15781,7 +15775,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -15801,10 +15795,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15827,7 +15821,7 @@
         <v>75</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
@@ -15880,7 +15874,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -15900,10 +15894,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -15926,7 +15920,7 @@
         <v>75</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" s="2"/>
@@ -15979,7 +15973,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -15999,10 +15993,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -16025,7 +16019,7 @@
         <v>75</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" s="2"/>
@@ -16078,7 +16072,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -16098,10 +16092,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16124,7 +16118,7 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L138" s="2"/>
       <c r="M138" s="2"/>
@@ -16177,7 +16171,7 @@
         <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -16197,10 +16191,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16223,7 +16217,7 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" s="2"/>
@@ -16276,7 +16270,7 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -16296,13 +16290,13 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D140" t="s" s="2">
         <v>75</v>
@@ -16324,13 +16318,13 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -16381,7 +16375,7 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
@@ -16401,10 +16395,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16502,10 +16496,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16603,10 +16597,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -16704,10 +16698,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -16805,10 +16799,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -16908,10 +16902,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17011,10 +17005,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17114,10 +17108,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17217,10 +17211,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17318,10 +17312,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17358,7 +17352,7 @@
         <v>75</v>
       </c>
       <c r="S150" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="T150" t="s" s="2">
         <v>75</v>
@@ -17377,7 +17371,7 @@
       </c>
       <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>75</v>
@@ -17395,7 +17389,7 @@
         <v>75</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>76</v>
@@ -17415,10 +17409,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17445,7 +17439,7 @@
       </c>
       <c r="L151" s="2"/>
       <c r="M151" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -17496,7 +17490,7 @@
         <v>75</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -17516,10 +17510,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17546,12 +17540,12 @@
       </c>
       <c r="L152" s="2"/>
       <c r="M152" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Q152" s="2"/>
       <c r="R152" t="s" s="2">
@@ -17597,7 +17591,7 @@
         <v>75</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -17617,10 +17611,10 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -17696,7 +17690,7 @@
         <v>75</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
@@ -17716,10 +17710,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17742,7 +17736,7 @@
         <v>75</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
@@ -17795,7 +17789,7 @@
         <v>75</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -17815,10 +17809,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17841,7 +17835,7 @@
         <v>75</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="L155" s="2"/>
       <c r="M155" s="2"/>
@@ -17894,7 +17888,7 @@
         <v>75</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -17914,10 +17908,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -17940,7 +17934,7 @@
         <v>75</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L156" s="2"/>
       <c r="M156" s="2"/>
@@ -17993,7 +17987,7 @@
         <v>75</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>81</v>
@@ -18013,10 +18007,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18039,7 +18033,7 @@
         <v>75</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -18092,7 +18086,7 @@
         <v>75</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
@@ -18112,10 +18106,10 @@
     </row>
     <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -18138,7 +18132,7 @@
         <v>75</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -18191,7 +18185,7 @@
         <v>75</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -18211,10 +18205,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18237,7 +18231,7 @@
         <v>75</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -18290,7 +18284,7 @@
         <v>75</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -18310,10 +18304,10 @@
     </row>
     <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18336,7 +18330,7 @@
         <v>75</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
@@ -18389,7 +18383,7 @@
         <v>75</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -18409,10 +18403,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18435,7 +18429,7 @@
         <v>75</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
@@ -18488,7 +18482,7 @@
         <v>75</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
@@ -18508,10 +18502,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18534,7 +18528,7 @@
         <v>75</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -18587,7 +18581,7 @@
         <v>75</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -18607,10 +18601,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18633,7 +18627,7 @@
         <v>75</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
@@ -18686,7 +18680,7 @@
         <v>75</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -18706,10 +18700,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18732,7 +18726,7 @@
         <v>75</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
@@ -18785,7 +18779,7 @@
         <v>75</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -18805,13 +18799,13 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D165" t="s" s="2">
         <v>75</v>
@@ -18833,13 +18827,13 @@
         <v>75</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -18890,7 +18884,7 @@
         <v>75</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -18910,10 +18904,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19011,10 +19005,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19112,10 +19106,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19213,10 +19207,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -19314,10 +19308,10 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -19417,10 +19411,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19520,10 +19514,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19623,10 +19617,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19726,10 +19720,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19827,10 +19821,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19867,7 +19861,7 @@
         <v>75</v>
       </c>
       <c r="S175" t="s" s="2">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="T175" t="s" s="2">
         <v>75</v>
@@ -19886,7 +19880,7 @@
       </c>
       <c r="Y175" s="2"/>
       <c r="Z175" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>75</v>
@@ -19904,7 +19898,7 @@
         <v>75</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>76</v>
@@ -19924,10 +19918,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -19954,7 +19948,7 @@
       </c>
       <c r="L176" s="2"/>
       <c r="M176" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -20005,7 +19999,7 @@
         <v>75</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -20025,10 +20019,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20055,12 +20049,12 @@
       </c>
       <c r="L177" s="2"/>
       <c r="M177" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Q177" s="2"/>
       <c r="R177" t="s" s="2">
@@ -20106,7 +20100,7 @@
         <v>75</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
@@ -20126,10 +20120,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20205,7 +20199,7 @@
         <v>75</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
@@ -20225,10 +20219,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20251,7 +20245,7 @@
         <v>75</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
@@ -20304,7 +20298,7 @@
         <v>75</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -20324,10 +20318,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20350,7 +20344,7 @@
         <v>75</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="L180" s="2"/>
       <c r="M180" s="2"/>
@@ -20403,7 +20397,7 @@
         <v>75</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -20423,10 +20417,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20449,7 +20443,7 @@
         <v>75</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="L181" s="2"/>
       <c r="M181" s="2"/>
@@ -20502,7 +20496,7 @@
         <v>75</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -20522,10 +20516,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20548,7 +20542,7 @@
         <v>75</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L182" s="2"/>
       <c r="M182" s="2"/>
@@ -20601,7 +20595,7 @@
         <v>75</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -20621,10 +20615,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20647,7 +20641,7 @@
         <v>75</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="L183" s="2"/>
       <c r="M183" s="2"/>
@@ -20700,7 +20694,7 @@
         <v>75</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -20720,10 +20714,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20746,7 +20740,7 @@
         <v>75</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
@@ -20799,7 +20793,7 @@
         <v>75</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>81</v>
@@ -20819,10 +20813,10 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -20845,7 +20839,7 @@
         <v>75</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
@@ -20898,7 +20892,7 @@
         <v>75</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>81</v>
@@ -20918,10 +20912,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -20944,7 +20938,7 @@
         <v>75</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
@@ -20997,7 +20991,7 @@
         <v>75</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>81</v>
@@ -21017,10 +21011,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21043,7 +21037,7 @@
         <v>75</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
@@ -21096,7 +21090,7 @@
         <v>75</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>81</v>
@@ -21116,10 +21110,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21142,7 +21136,7 @@
         <v>75</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
@@ -21195,7 +21189,7 @@
         <v>75</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>81</v>
@@ -21215,10 +21209,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21241,7 +21235,7 @@
         <v>75</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
@@ -21294,7 +21288,7 @@
         <v>75</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>81</v>
@@ -21314,13 +21308,13 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D190" t="s" s="2">
         <v>75</v>
@@ -21342,13 +21336,13 @@
         <v>75</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="N190" s="2"/>
       <c r="O190" s="2"/>
@@ -21399,7 +21393,7 @@
         <v>75</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>81</v>
@@ -21419,10 +21413,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21520,10 +21514,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21621,10 +21615,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21722,10 +21716,10 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
@@ -21823,10 +21817,10 @@
     </row>
     <row r="195" hidden="true">
       <c r="A195" t="s" s="2">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" t="s" s="2">
@@ -21926,10 +21920,10 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
@@ -22029,10 +22023,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22132,10 +22126,10 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
@@ -22235,10 +22229,10 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
@@ -22336,10 +22330,10 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
@@ -22376,7 +22370,7 @@
         <v>75</v>
       </c>
       <c r="S200" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="T200" t="s" s="2">
         <v>75</v>
@@ -22395,7 +22389,7 @@
       </c>
       <c r="Y200" s="2"/>
       <c r="Z200" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AA200" t="s" s="2">
         <v>75</v>
@@ -22413,7 +22407,7 @@
         <v>75</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>76</v>
@@ -22433,10 +22427,10 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
@@ -22463,7 +22457,7 @@
       </c>
       <c r="L201" s="2"/>
       <c r="M201" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
@@ -22514,7 +22508,7 @@
         <v>75</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>81</v>
@@ -22534,10 +22528,10 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
@@ -22564,12 +22558,12 @@
       </c>
       <c r="L202" s="2"/>
       <c r="M202" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Q202" s="2"/>
       <c r="R202" t="s" s="2">
@@ -22615,7 +22609,7 @@
         <v>75</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>81</v>
@@ -22635,10 +22629,10 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
@@ -22714,7 +22708,7 @@
         <v>75</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>81</v>
@@ -22734,10 +22728,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -22760,7 +22754,7 @@
         <v>75</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="L204" s="2"/>
       <c r="M204" s="2"/>
@@ -22813,7 +22807,7 @@
         <v>75</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG204" t="s" s="2">
         <v>81</v>
@@ -22833,10 +22827,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -22859,7 +22853,7 @@
         <v>75</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="L205" s="2"/>
       <c r="M205" s="2"/>
@@ -22912,7 +22906,7 @@
         <v>75</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG205" t="s" s="2">
         <v>81</v>
@@ -22932,10 +22926,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -22958,7 +22952,7 @@
         <v>75</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="L206" s="2"/>
       <c r="M206" s="2"/>
@@ -23011,7 +23005,7 @@
         <v>75</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>81</v>
@@ -23031,10 +23025,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -23057,7 +23051,7 @@
         <v>75</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L207" s="2"/>
       <c r="M207" s="2"/>
@@ -23110,7 +23104,7 @@
         <v>75</v>
       </c>
       <c r="AF207" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AG207" t="s" s="2">
         <v>81</v>
@@ -23130,10 +23124,10 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C208" s="2"/>
       <c r="D208" t="s" s="2">
@@ -23156,7 +23150,7 @@
         <v>75</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="L208" s="2"/>
       <c r="M208" s="2"/>
@@ -23209,7 +23203,7 @@
         <v>75</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>81</v>
@@ -23229,10 +23223,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23255,7 +23249,7 @@
         <v>75</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L209" s="2"/>
       <c r="M209" s="2"/>
@@ -23308,7 +23302,7 @@
         <v>75</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AG209" t="s" s="2">
         <v>81</v>
@@ -23328,10 +23322,10 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C210" s="2"/>
       <c r="D210" t="s" s="2">
@@ -23354,7 +23348,7 @@
         <v>75</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L210" s="2"/>
       <c r="M210" s="2"/>
@@ -23407,7 +23401,7 @@
         <v>75</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>81</v>
@@ -23427,10 +23421,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23453,7 +23447,7 @@
         <v>75</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L211" s="2"/>
       <c r="M211" s="2"/>
@@ -23506,7 +23500,7 @@
         <v>75</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>81</v>
@@ -23526,10 +23520,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23552,7 +23546,7 @@
         <v>75</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="L212" s="2"/>
       <c r="M212" s="2"/>
@@ -23605,7 +23599,7 @@
         <v>75</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>81</v>
@@ -23625,10 +23619,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23651,7 +23645,7 @@
         <v>75</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L213" s="2"/>
       <c r="M213" s="2"/>
@@ -23704,7 +23698,7 @@
         <v>75</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>81</v>
@@ -23724,10 +23718,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -23750,7 +23744,7 @@
         <v>75</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L214" s="2"/>
       <c r="M214" s="2"/>
@@ -23803,7 +23797,7 @@
         <v>75</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>81</v>
@@ -23823,13 +23817,13 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="D215" t="s" s="2">
         <v>75</v>
@@ -23851,13 +23845,13 @@
         <v>75</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="L215" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="N215" s="2"/>
       <c r="O215" s="2"/>
@@ -23908,7 +23902,7 @@
         <v>75</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>81</v>
@@ -23928,10 +23922,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24029,10 +24023,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24130,10 +24124,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24231,10 +24225,10 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
@@ -24332,10 +24326,10 @@
     </row>
     <row r="220" hidden="true">
       <c r="A220" t="s" s="2">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C220" s="2"/>
       <c r="D220" t="s" s="2">
@@ -24435,10 +24429,10 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
@@ -24538,10 +24532,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24641,10 +24635,10 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
@@ -24744,10 +24738,10 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
@@ -24845,10 +24839,10 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
@@ -24885,7 +24879,7 @@
         <v>75</v>
       </c>
       <c r="S225" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="T225" t="s" s="2">
         <v>75</v>
@@ -24904,7 +24898,7 @@
       </c>
       <c r="Y225" s="2"/>
       <c r="Z225" t="s" s="2">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="AA225" t="s" s="2">
         <v>75</v>
@@ -24922,7 +24916,7 @@
         <v>75</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>76</v>
@@ -24942,10 +24936,10 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
@@ -24972,7 +24966,7 @@
       </c>
       <c r="L226" s="2"/>
       <c r="M226" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -25023,7 +25017,7 @@
         <v>75</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>81</v>
@@ -25043,10 +25037,10 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
@@ -25073,12 +25067,12 @@
       </c>
       <c r="L227" s="2"/>
       <c r="M227" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="N227" s="2"/>
       <c r="O227" s="2"/>
       <c r="P227" t="s" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="Q227" s="2"/>
       <c r="R227" t="s" s="2">
@@ -25124,7 +25118,7 @@
         <v>75</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>81</v>
@@ -25144,10 +25138,10 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
@@ -25223,7 +25217,7 @@
         <v>75</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>81</v>
@@ -25243,10 +25237,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -25269,7 +25263,7 @@
         <v>75</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="L229" s="2"/>
       <c r="M229" s="2"/>
@@ -25322,7 +25316,7 @@
         <v>75</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="AG229" t="s" s="2">
         <v>81</v>
@@ -25342,10 +25336,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -25368,7 +25362,7 @@
         <v>75</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="L230" s="2"/>
       <c r="M230" s="2"/>
@@ -25421,7 +25415,7 @@
         <v>75</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="AG230" t="s" s="2">
         <v>81</v>
@@ -25441,10 +25435,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -25467,7 +25461,7 @@
         <v>75</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="L231" s="2"/>
       <c r="M231" s="2"/>
@@ -25520,7 +25514,7 @@
         <v>75</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>81</v>
@@ -25540,10 +25534,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -25566,7 +25560,7 @@
         <v>75</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="L232" s="2"/>
       <c r="M232" s="2"/>
@@ -25619,7 +25613,7 @@
         <v>75</v>
       </c>
       <c r="AF232" t="s" s="2">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="AG232" t="s" s="2">
         <v>81</v>
@@ -25639,10 +25633,10 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" t="s" s="2">
@@ -25665,7 +25659,7 @@
         <v>75</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="L233" s="2"/>
       <c r="M233" s="2"/>
@@ -25718,7 +25712,7 @@
         <v>75</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>81</v>
@@ -25738,10 +25732,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -25764,7 +25758,7 @@
         <v>75</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="L234" s="2"/>
       <c r="M234" s="2"/>
@@ -25817,7 +25811,7 @@
         <v>75</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="AG234" t="s" s="2">
         <v>81</v>
@@ -25837,10 +25831,10 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C235" s="2"/>
       <c r="D235" t="s" s="2">
@@ -25863,7 +25857,7 @@
         <v>75</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="L235" s="2"/>
       <c r="M235" s="2"/>
@@ -25916,7 +25910,7 @@
         <v>75</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>81</v>
@@ -25936,10 +25930,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -25962,7 +25956,7 @@
         <v>75</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="L236" s="2"/>
       <c r="M236" s="2"/>
@@ -26015,7 +26009,7 @@
         <v>75</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>81</v>
@@ -26035,10 +26029,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -26061,7 +26055,7 @@
         <v>75</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="L237" s="2"/>
       <c r="M237" s="2"/>
@@ -26114,7 +26108,7 @@
         <v>75</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>81</v>
@@ -26134,10 +26128,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -26160,7 +26154,7 @@
         <v>75</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="L238" s="2"/>
       <c r="M238" s="2"/>
@@ -26213,7 +26207,7 @@
         <v>75</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>81</v>
@@ -26233,10 +26227,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -26259,7 +26253,7 @@
         <v>75</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="L239" s="2"/>
       <c r="M239" s="2"/>
@@ -26312,7 +26306,7 @@
         <v>75</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>81</v>
@@ -26332,10 +26326,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -26358,7 +26352,7 @@
         <v>75</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="L240" s="2"/>
       <c r="M240" s="2"/>
@@ -26411,7 +26405,7 @@
         <v>75</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>81</v>
@@ -26431,10 +26425,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -26457,7 +26451,7 @@
         <v>75</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="L241" s="2"/>
       <c r="M241" s="2"/>
@@ -26510,7 +26504,7 @@
         <v>75</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>81</v>
@@ -26530,10 +26524,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -26556,7 +26550,7 @@
         <v>75</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="L242" s="2"/>
       <c r="M242" s="2"/>
@@ -26609,7 +26603,7 @@
         <v>75</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>81</v>
@@ -26629,10 +26623,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -26655,7 +26649,7 @@
         <v>75</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="L243" s="2"/>
       <c r="M243" s="2"/>
@@ -26708,7 +26702,7 @@
         <v>75</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>81</v>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:04:35+00:00</t>
+    <t>2026-07-29T08:58:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T08:58:09+00:00</t>
+    <t>2026-07-29T09:37:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/enrichissement-pharm/ig/StructureDefinition-fr-cda-acte.xlsx
+++ b/enrichissement-pharm/ig/StructureDefinition-fr-cda-acte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:37:21+00:00</t>
+    <t>2026-08-03T10:14:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
